--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999991</v>
       </c>
       <c r="B2" t="n">
-        <v>58155</v>
+        <v>58158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128999797</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128999327</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R7" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,6 +1245,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,22 +1264,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999670</v>
+        <v>128999607</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,37 +1287,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489252</v>
+        <v>489250</v>
       </c>
       <c r="R8" t="n">
-        <v>6834528</v>
+        <v>6834522</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1361,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
         <v>128999750</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128999293</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128999797</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128999327</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999670</v>
+        <v>128999607</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489252</v>
+        <v>489250</v>
       </c>
       <c r="R7" t="n">
-        <v>6834528</v>
+        <v>6834522</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,11 +1245,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1264,22 +1259,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,37 +1282,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R8" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1347,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1361,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
         <v>128999750</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128999293</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999797</v>
+        <v>128999327</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489206</v>
+        <v>489143</v>
       </c>
       <c r="R3" t="n">
-        <v>6834547</v>
+        <v>6834576</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999327</v>
+        <v>128999797</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -900,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489143</v>
+        <v>489206</v>
       </c>
       <c r="R4" t="n">
-        <v>6834576</v>
+        <v>6834547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999991</v>
       </c>
       <c r="B2" t="n">
-        <v>58158</v>
+        <v>58160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999327</v>
+        <v>128999797</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489143</v>
+        <v>489206</v>
       </c>
       <c r="R3" t="n">
-        <v>6834576</v>
+        <v>6834547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999797</v>
+        <v>128999327</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489206</v>
+        <v>489143</v>
       </c>
       <c r="R4" t="n">
-        <v>6834547</v>
+        <v>6834576</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128999607</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128999670</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>128999750</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128999293</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R7" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,6 +1245,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,22 +1264,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999670</v>
+        <v>128999607</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,37 +1287,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489252</v>
+        <v>489250</v>
       </c>
       <c r="R8" t="n">
-        <v>6834528</v>
+        <v>6834522</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1361,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999991</v>
       </c>
       <c r="B2" t="n">
-        <v>58160</v>
+        <v>58162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128999797</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128999327</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128999670</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>128999607</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>128999750</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128999293</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999670</v>
+        <v>128999607</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489252</v>
+        <v>489250</v>
       </c>
       <c r="R7" t="n">
-        <v>6834528</v>
+        <v>6834522</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,11 +1245,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1264,22 +1259,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,37 +1282,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R8" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1347,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1361,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128999797</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128999327</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R7" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,6 +1245,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,22 +1264,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999670</v>
+        <v>128999607</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,37 +1287,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489252</v>
+        <v>489250</v>
       </c>
       <c r="R8" t="n">
-        <v>6834528</v>
+        <v>6834522</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1361,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
         <v>128999750</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128999293</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128999797</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128999327</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>128999607</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>128999750</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128999293</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999670</v>
+        <v>128999607</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489252</v>
+        <v>489250</v>
       </c>
       <c r="R7" t="n">
-        <v>6834528</v>
+        <v>6834522</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,11 +1245,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1264,22 +1259,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,37 +1282,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R8" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1347,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1361,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R7" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,6 +1245,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,22 +1264,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999670</v>
+        <v>128999607</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,37 +1287,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489252</v>
+        <v>489250</v>
       </c>
       <c r="R8" t="n">
-        <v>6834528</v>
+        <v>6834522</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1361,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128999360</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128999721</v>
       </c>
       <c r="B6" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999670</v>
+        <v>128999607</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489252</v>
+        <v>489250</v>
       </c>
       <c r="R7" t="n">
-        <v>6834528</v>
+        <v>6834522</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,11 +1245,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1264,22 +1259,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,37 +1282,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R8" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1347,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1361,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>128999242</v>
       </c>
       <c r="B10" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128999381</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999991</v>
+        <v>128999293</v>
       </c>
       <c r="B2" t="n">
-        <v>58162</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102999</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489247</v>
+        <v>489153</v>
       </c>
       <c r="R2" t="n">
-        <v>6834495</v>
+        <v>6834611</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999797</v>
+        <v>128999327</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489206</v>
+        <v>489143</v>
       </c>
       <c r="R3" t="n">
-        <v>6834547</v>
+        <v>6834576</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,26 +857,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999327</v>
+        <v>128999607</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489143</v>
+        <v>489250</v>
       </c>
       <c r="R4" t="n">
-        <v>6834576</v>
+        <v>6834522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128999360</v>
+        <v>128999750</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,46 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489294</v>
+        <v>489220</v>
       </c>
       <c r="R5" t="n">
-        <v>6834484</v>
+        <v>6834501</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128999721</v>
+        <v>128999797</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489252</v>
+        <v>489206</v>
       </c>
       <c r="R6" t="n">
-        <v>6834528</v>
+        <v>6834547</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,11 +1136,6 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1162,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128999607</v>
+        <v>128999670</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489250</v>
+        <v>489252</v>
       </c>
       <c r="R7" t="n">
-        <v>6834522</v>
+        <v>6834528</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,22 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128999670</v>
+        <v>128999991</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>58393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,13 +1297,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489252</v>
+        <v>489247</v>
       </c>
       <c r="R8" t="n">
-        <v>6834528</v>
+        <v>6834495</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,48 +1359,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128999750</v>
+        <v>128999360</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Dlr</t>
+          <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489220</v>
+        <v>489294</v>
       </c>
       <c r="R9" t="n">
-        <v>6834501</v>
+        <v>6834484</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,45 +1465,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128999242</v>
+        <v>128999381</v>
       </c>
       <c r="B10" t="n">
-        <v>97598</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489166</v>
+        <v>489291</v>
       </c>
       <c r="R10" t="n">
-        <v>6834639</v>
+        <v>6834488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1555,12 +1559,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1570,7 +1574,7 @@
         <v>128999843</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,54 +1677,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128999381</v>
+        <v>128999242</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olovsbacken, Olovsbacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489291</v>
+        <v>489166</v>
       </c>
       <c r="R12" t="n">
-        <v>6834488</v>
+        <v>6834639</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1767,57 +1762,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128999293</v>
+        <v>128999721</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Olovsbacken, Olovsbacken, Dlr</t>
+          <t>Lillhamra, Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489153</v>
+        <v>489252</v>
       </c>
       <c r="R13" t="n">
-        <v>6834611</v>
+        <v>6834528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,6 +1845,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 42179-2025 artfynd.xlsx
+++ b/artfynd/A 42179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999293</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999327</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999607</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999750</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999797</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999670</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999991</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999360</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1568,6 +1613,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999381</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999843</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999242</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,8 +1933,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999721</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>